--- a/astro-site/public/dl/plan-catering-tematico-eventos/calculadora-pricing-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/calculadora-pricing-catering-tematico-eventos.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora pricing" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 ejemplos validados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Calculadora pricing'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'10 ejemplos validados'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -531,7 +534,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -557,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -726,6 +730,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -741,7 +746,7 @@
       </c>
       <c r="B17" s="7">
         <f>IF(B5="B2B", IF(B6&lt;40, 65, IF(B6&lt;100, 55, 48)), IF(B6&lt;40, 58, IF(B6&lt;80, 48, 42)))</f>
-        <v/>
+        <v>55.0</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -757,7 +762,7 @@
       </c>
       <c r="B18" s="9">
         <f>IF(B10="exclusivo",1.55,IF(B10="premium",1.25,1.00))</f>
-        <v/>
+        <v>1.25</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
@@ -773,7 +778,7 @@
       </c>
       <c r="B19" s="9">
         <f>IF(B8&gt;=4,1.32,IF(B8=3,1.18,IF(B8=2,1.08,1.00)))</f>
-        <v/>
+        <v>1.18</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -789,7 +794,7 @@
       </c>
       <c r="B20" s="9">
         <f>IF(OR(B9="japonés",B9="marisquería",B9="indio"),1.18,IF(OR(B9="peruano",B9="vegano"),1.10,1.00))</f>
-        <v/>
+        <v>1.18</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -805,7 +810,7 @@
       </c>
       <c r="B21" s="9">
         <f>IF(B13="sí",1.12,1.00)</f>
-        <v/>
+        <v>1.12</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -821,7 +826,7 @@
       </c>
       <c r="B22" s="7">
         <f>IF(B11="sí",14,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
@@ -837,7 +842,7 @@
       </c>
       <c r="B23" s="9">
         <f>IF(B12="sí",280,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
@@ -853,7 +858,7 @@
       </c>
       <c r="B24" s="7">
         <f>B7*0.95*2</f>
-        <v/>
+        <v>66.5</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
@@ -869,7 +874,7 @@
       </c>
       <c r="B25" s="7">
         <f>B14*135</f>
-        <v/>
+        <v>270.0</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
@@ -877,6 +882,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -892,7 +898,7 @@
       </c>
       <c r="B28" s="11">
         <f>B17*B18*B19*B20*B21+B22</f>
-        <v/>
+        <v>107.2148</v>
       </c>
     </row>
     <row r="29">
@@ -903,7 +909,7 @@
       </c>
       <c r="B29" s="11">
         <f>B28*B6</f>
-        <v/>
+        <v>8577.184</v>
       </c>
     </row>
     <row r="30">
@@ -914,7 +920,7 @@
       </c>
       <c r="B30" s="11">
         <f>B23+B24+B25</f>
-        <v/>
+        <v>336.5</v>
       </c>
     </row>
     <row r="31">
@@ -925,7 +931,7 @@
       </c>
       <c r="B31" s="12">
         <f>B29+B30</f>
-        <v/>
+        <v>8913.684</v>
       </c>
     </row>
     <row r="32">
@@ -936,7 +942,7 @@
       </c>
       <c r="B32" s="11">
         <f>B31/B6</f>
-        <v/>
+        <v>111.42105</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +953,7 @@
       </c>
       <c r="B33" s="13">
         <f>B31*0.4</f>
-        <v/>
+        <v>3565.4736</v>
       </c>
     </row>
     <row r="34">
@@ -958,7 +964,7 @@
       </c>
       <c r="B34" s="11">
         <f>B31*0.55</f>
-        <v/>
+        <v>4902.5262</v>
       </c>
     </row>
     <row r="35">
@@ -973,32 +979,41 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="C6:E6"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1006,7 +1021,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1036,6 +1051,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1455,9 +1471,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>